--- a/项目清单.xlsx
+++ b/项目清单.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="83">
   <si>
     <t>启用</t>
   </si>
@@ -69,6 +69,9 @@
     <t>详情图片（分号隔开）</t>
   </si>
   <si>
+    <t>加载底图</t>
+  </si>
+  <si>
     <t>是</t>
   </si>
   <si>
@@ -94,11 +97,14 @@
   </si>
   <si>
     <t>assets/images/project-01/detail-01.jpg;</t>
+  </si>
+  <si>
+    <t>assets/images/placeholders/project-01.jpg</t>
   </si>
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="1100"/>
         <color rgb="FF1B1B19"/>
         <rFont val="Carlito"/>
         <charset val="134"/>
@@ -107,7 +113,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="1100"/>
         <color rgb="FF1B1B19"/>
         <rFont val="宋体"/>
         <charset val="134"/>
@@ -134,9 +140,12 @@
     <t/>
   </si>
   <si>
+    <t>assets/images/placeholders/project-02.jpg</t>
+  </si>
+  <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="1100"/>
         <color rgb="FF1B1B19"/>
         <rFont val="Carlito"/>
         <charset val="134"/>
@@ -145,7 +154,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="1100"/>
         <color rgb="FF1B1B19"/>
         <rFont val="宋体"/>
         <charset val="134"/>
@@ -166,6 +175,9 @@
     <t>assets/images/project-03/cover.jpg</t>
   </si>
   <si>
+    <t>assets/images/placeholders/project-03.jpg</t>
+  </si>
+  <si>
     <t>Animation Practice 01</t>
   </si>
   <si>
@@ -177,7 +189,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="1100"/>
         <color rgb="FF1B1B19"/>
         <rFont val="宋体"/>
         <charset val="134"/>
@@ -186,7 +198,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="1100"/>
         <color rgb="FF1B1B19"/>
         <rFont val="Carlito"/>
         <charset val="134"/>
@@ -201,6 +213,9 @@
     <t>assets/images/project-04/cover.jpg</t>
   </si>
   <si>
+    <t>assets/images/placeholders/project-04.jpg</t>
+  </si>
+  <si>
     <t>雨天遮罩</t>
   </si>
   <si>
@@ -214,11 +229,14 @@
   </si>
   <si>
     <t>assets/images/project-05/cover.jpg</t>
+  </si>
+  <si>
+    <t>assets/images/placeholders/project-05.jpg</t>
   </si>
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="1100"/>
         <color rgb="FF1B1B19"/>
         <rFont val="宋体"/>
         <charset val="134"/>
@@ -227,7 +245,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="1100"/>
         <color rgb="FF1B1B19"/>
         <rFont val="Carlito"/>
         <charset val="134"/>
@@ -236,7 +254,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="1100"/>
         <color rgb="FF1B1B19"/>
         <rFont val="宋体"/>
         <charset val="134"/>
@@ -253,7 +271,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="1100"/>
         <color rgb="FF1B1B19"/>
         <rFont val="Carlito"/>
         <charset val="134"/>
@@ -262,7 +280,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="1100"/>
         <color rgb="FF1B1B19"/>
         <rFont val="宋体"/>
         <charset val="134"/>
@@ -271,7 +289,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="1100"/>
         <color rgb="FF1B1B19"/>
         <rFont val="Carlito"/>
         <charset val="134"/>
@@ -280,7 +298,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="1100"/>
         <color rgb="FF1B1B19"/>
         <rFont val="宋体"/>
         <charset val="134"/>
@@ -289,7 +307,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="1100"/>
         <color rgb="FF1B1B19"/>
         <rFont val="Carlito"/>
         <charset val="134"/>
@@ -298,7 +316,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="1100"/>
         <color rgb="FF1B1B19"/>
         <rFont val="宋体"/>
         <charset val="134"/>
@@ -313,6 +331,9 @@
     <t>assets/images/project-06/cover.jpg</t>
   </si>
   <si>
+    <t>assets/images/placeholders/project-06.jpg</t>
+  </si>
+  <si>
     <t>作品网站项目清单</t>
   </si>
   <si>
@@ -349,10 +370,34 @@
     <t>5</t>
   </si>
   <si>
+    <t>“加载底图”留空时使用网站自带的默认渐变。</t>
+  </si>
+  <si>
+    <t>底图颜色</t>
+  </si>
+  <si>
+    <t>填写颜色，例如 #d8d3c8、rgb(216, 211, 200) 或 hsl(42, 17%, 82%)。</t>
+  </si>
+  <si>
+    <t>底图渐变</t>
+  </si>
+  <si>
+    <t>填写 CSS 渐变，例如 linear-gradient(135deg, #d9ddd5, #6f8076)。</t>
+  </si>
+  <si>
+    <t>底图图片</t>
+  </si>
+  <si>
+    <t>填写相对路径，例如 assets/images/placeholders/project-01.jpg。路径建议使用 /。</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
     <t>保存并关闭 Excel，双击网站目录中的“更新网站数据.bat”。</t>
   </si>
   <si>
-    <t>6</t>
+    <t>7</t>
   </si>
   <si>
     <t>刷新 index.html 预览；确认后使用 GitHub Desktop 提交并推送。</t>
@@ -375,7 +420,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="00"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -419,30 +464,24 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -450,15 +489,13 @@
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -466,7 +503,6 @@
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -474,7 +510,6 @@
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -482,88 +517,82 @@
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <sz val="1100"/>
+      <color rgb="FF1B1B19"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="1100"/>
+      <color rgb="FF1B1B19"/>
+      <name val="Carlito"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="36">
@@ -641,19 +670,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -665,19 +694,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -689,19 +718,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -713,19 +742,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -737,19 +766,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -761,19 +790,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -801,7 +830,9 @@
       <left style="thin">
         <color rgb="FFD8D2C5"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color rgb="FFD8D2C5"/>
+      </right>
       <top/>
       <bottom style="thin">
         <color rgb="FFD8D2C5"/>
@@ -816,6 +847,32 @@
       <top style="thin">
         <color rgb="FFD8D2C5"/>
       </top>
+      <bottom style="thin">
+        <color rgb="FFD8D2C5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD8D2C5"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD8D2C5"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD8D2C5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD8D2C5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD8D2C5"/>
+      </left>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FFD8D2C5"/>
       </bottom>
@@ -849,7 +906,9 @@
       <left style="thin">
         <color rgb="FFD8D2C5"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color rgb="FFD8D2C5"/>
+      </right>
       <top style="thin">
         <color rgb="FFD8D2C5"/>
       </top>
@@ -860,37 +919,7 @@
       <left style="thin">
         <color rgb="FFD8D2C5"/>
       </left>
-      <right style="thin">
-        <color rgb="FFD8D2C5"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFD8D2C5"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD8D2C5"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD8D2C5"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD8D2C5"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD8D2C5"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD8D2C5"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD8D2C5"/>
-      </right>
+      <right/>
       <top style="thin">
         <color rgb="FFD8D2C5"/>
       </top>
@@ -926,7 +955,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4" tint="0.49998"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1075,10 +1104,10 @@
     <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1087,10 +1116,10 @@
     <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1099,10 +1128,10 @@
     <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1111,10 +1140,10 @@
     <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1123,10 +1152,10 @@
     <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1135,10 +1164,10 @@
     <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1151,84 +1180,84 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="4" borderId="7" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="4" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="4" borderId="7" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="4" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="4" borderId="7" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="4" fillId="4" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="1" fontId="4" fillId="4" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="4" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="4" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="1" fontId="4" fillId="4" borderId="8" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="176" fontId="4" fillId="4" borderId="8" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="4" fillId="4" borderId="8" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="4" borderId="9" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="4" borderId="9" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="4" borderId="9" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1523,9 +1552,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ProjectsTable" displayName="ProjectsTable" ref="A1:M7" totalsRowShown="0">
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:M7" etc:filterBottomFollowUsedRange="0"/>
-  <tableColumns count="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ProjectsTable" displayName="ProjectsTable" ref="A1:N7" totalsRowShown="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:N7" etc:filterBottomFollowUsedRange="0"/>
+  <tableColumns count="14">
     <tableColumn id="1" name="启用"/>
     <tableColumn id="2" name="排序"/>
     <tableColumn id="3" name="编号"/>
@@ -1539,6 +1568,7 @@
     <tableColumn id="11" name="视频路径"/>
     <tableColumn id="12" name="封面路径"/>
     <tableColumn id="13" name="详情图片（分号隔开）"/>
+    <tableColumn id="14" name="加载底图"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1739,7 +1769,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M100"/>
+  <dimension ref="A1:N100"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="3" width="8" customWidth="1"/>
@@ -1751,93 +1781,100 @@
     <col min="9" max="10" width="42" customWidth="1"/>
     <col min="11" max="12" width="36" customWidth="1"/>
     <col min="13" max="13" width="44" customWidth="1"/>
+    <col min="14" max="14" width="48" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:13">
-      <c r="A1" s="8" t="s">
+    <row r="1" ht="28" customHeight="1" spans="1:14">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="L1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="M1" s="6" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" ht="55" customHeight="1" spans="1:13">
-      <c r="A2" s="9" t="s">
+      <c r="N1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="10">
+    </row>
+    <row r="2" ht="55" customHeight="1" spans="1:14">
+      <c r="A2" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="9">
         <v>1</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="10">
         <v>1</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="12">
+        <v>2026</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2" s="15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" ht="55" customHeight="1" spans="1:14">
+      <c r="A3" s="16" t="s">
         <v>14</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="13">
-        <v>2026</v>
-      </c>
-      <c r="H2" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="L2" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="M2" s="15" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" ht="55" customHeight="1" spans="1:13">
-      <c r="A3" s="16" t="s">
-        <v>13</v>
       </c>
       <c r="B3" s="17">
         <v>2</v>
@@ -1846,37 +1883,40 @@
         <v>2</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E3" s="19"/>
       <c r="F3" s="19" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G3" s="20">
         <v>2025</v>
       </c>
-      <c r="H3" s="12" t="s">
-        <v>16</v>
+      <c r="H3" s="11" t="s">
+        <v>17</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J3" s="19" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K3" s="19" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L3" s="19" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M3" s="22" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" ht="55" customHeight="1" spans="1:13">
+        <v>30</v>
+      </c>
+      <c r="N3" s="15" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" ht="55" customHeight="1" spans="1:14">
       <c r="A4" s="16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4" s="17">
         <v>3</v>
@@ -1885,35 +1925,38 @@
         <v>3</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E4" s="19"/>
       <c r="F4" s="19" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G4" s="20">
         <v>2025</v>
       </c>
       <c r="H4" s="19" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I4" s="19"/>
       <c r="J4" s="19" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K4" s="19" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="L4" s="19" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M4" s="22" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" ht="55" customHeight="1" spans="1:13">
+        <v>30</v>
+      </c>
+      <c r="N4" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" ht="55" customHeight="1" spans="1:14">
       <c r="A5" s="16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="17">
         <v>4</v>
@@ -1922,39 +1965,42 @@
         <v>4</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G5" s="20">
         <v>2024</v>
       </c>
       <c r="H5" s="19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I5" s="21" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J5" s="19" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K5" s="19" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="L5" s="19" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M5" s="22" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" ht="55" customHeight="1" spans="1:13">
+        <v>30</v>
+      </c>
+      <c r="N5" s="15" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" ht="55" customHeight="1" spans="1:14">
       <c r="A6" s="16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" s="17">
         <v>5</v>
@@ -1963,37 +2009,40 @@
         <v>5</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G6" s="20">
         <v>2024</v>
       </c>
       <c r="H6" s="19" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I6" s="19"/>
       <c r="J6" s="19" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K6" s="19" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="L6" s="19" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="M6" s="22" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" ht="55" customHeight="1" spans="1:13">
+        <v>30</v>
+      </c>
+      <c r="N6" s="15" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" ht="55" customHeight="1" spans="1:14">
       <c r="A7" s="23" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" s="24">
         <v>6</v>
@@ -2002,37 +2051,40 @@
         <v>6</v>
       </c>
       <c r="D7" s="26" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G7" s="28">
         <v>2023</v>
       </c>
       <c r="H7" s="19" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I7" s="27" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="J7" s="27" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K7" s="27" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L7" s="27" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="M7" s="29" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" ht="55" customHeight="1" spans="1:13">
+        <v>30</v>
+      </c>
+      <c r="N7" s="15" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" ht="55" customHeight="1" spans="1:14">
       <c r="A8" s="23"/>
       <c r="B8" s="24"/>
       <c r="C8" s="25"/>
@@ -2046,8 +2098,9 @@
       <c r="K8" s="27"/>
       <c r="L8" s="27"/>
       <c r="M8" s="29"/>
-    </row>
-    <row r="9" ht="55" customHeight="1" spans="1:13">
+      <c r="N8" s="15"/>
+    </row>
+    <row r="9" ht="55" customHeight="1" spans="1:14">
       <c r="A9" s="23"/>
       <c r="B9" s="24"/>
       <c r="C9" s="25"/>
@@ -2061,8 +2114,9 @@
       <c r="K9" s="27"/>
       <c r="L9" s="27"/>
       <c r="M9" s="29"/>
-    </row>
-    <row r="10" ht="55" customHeight="1" spans="1:13">
+      <c r="N9" s="15"/>
+    </row>
+    <row r="10" ht="55" customHeight="1" spans="1:14">
       <c r="A10" s="23"/>
       <c r="B10" s="24"/>
       <c r="C10" s="25"/>
@@ -2076,8 +2130,9 @@
       <c r="K10" s="27"/>
       <c r="L10" s="27"/>
       <c r="M10" s="29"/>
-    </row>
-    <row r="11" spans="1:13">
+      <c r="N10" s="15"/>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="30"/>
       <c r="B11" s="31"/>
       <c r="C11" s="32"/>
@@ -2091,8 +2146,9 @@
       <c r="K11" s="33"/>
       <c r="L11" s="33"/>
       <c r="M11" s="33"/>
-    </row>
-    <row r="12" spans="1:13">
+      <c r="N11" s="15"/>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="30"/>
       <c r="B12" s="31"/>
       <c r="C12" s="32"/>
@@ -2106,8 +2162,9 @@
       <c r="K12" s="33"/>
       <c r="L12" s="33"/>
       <c r="M12" s="33"/>
-    </row>
-    <row r="13" spans="1:13">
+      <c r="N12" s="15"/>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" s="30"/>
       <c r="B13" s="31"/>
       <c r="C13" s="32"/>
@@ -2121,8 +2178,9 @@
       <c r="K13" s="33"/>
       <c r="L13" s="33"/>
       <c r="M13" s="33"/>
-    </row>
-    <row r="14" spans="1:13">
+      <c r="N13" s="15"/>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" s="30"/>
       <c r="B14" s="31"/>
       <c r="C14" s="32"/>
@@ -2136,8 +2194,9 @@
       <c r="K14" s="33"/>
       <c r="L14" s="33"/>
       <c r="M14" s="33"/>
-    </row>
-    <row r="15" spans="1:13">
+      <c r="N14" s="15"/>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" s="30"/>
       <c r="B15" s="31"/>
       <c r="C15" s="32"/>
@@ -2151,8 +2210,9 @@
       <c r="K15" s="33"/>
       <c r="L15" s="33"/>
       <c r="M15" s="33"/>
-    </row>
-    <row r="16" spans="1:13">
+      <c r="N15" s="15"/>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" s="30"/>
       <c r="B16" s="31"/>
       <c r="C16" s="32"/>
@@ -2166,8 +2226,9 @@
       <c r="K16" s="33"/>
       <c r="L16" s="33"/>
       <c r="M16" s="33"/>
-    </row>
-    <row r="17" spans="1:13">
+      <c r="N16" s="15"/>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" s="30"/>
       <c r="B17" s="31"/>
       <c r="C17" s="32"/>
@@ -2181,8 +2242,9 @@
       <c r="K17" s="33"/>
       <c r="L17" s="33"/>
       <c r="M17" s="33"/>
-    </row>
-    <row r="18" spans="1:13">
+      <c r="N17" s="15"/>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" s="30"/>
       <c r="B18" s="31"/>
       <c r="C18" s="32"/>
@@ -2196,8 +2258,9 @@
       <c r="K18" s="33"/>
       <c r="L18" s="33"/>
       <c r="M18" s="33"/>
-    </row>
-    <row r="19" spans="1:13">
+      <c r="N18" s="15"/>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" s="30"/>
       <c r="B19" s="31"/>
       <c r="C19" s="32"/>
@@ -2211,8 +2274,9 @@
       <c r="K19" s="33"/>
       <c r="L19" s="33"/>
       <c r="M19" s="33"/>
-    </row>
-    <row r="20" spans="1:13">
+      <c r="N19" s="15"/>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" s="30"/>
       <c r="B20" s="31"/>
       <c r="C20" s="32"/>
@@ -2226,8 +2290,9 @@
       <c r="K20" s="33"/>
       <c r="L20" s="33"/>
       <c r="M20" s="33"/>
-    </row>
-    <row r="21" spans="1:13">
+      <c r="N20" s="15"/>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" s="30"/>
       <c r="B21" s="31"/>
       <c r="C21" s="32"/>
@@ -2241,8 +2306,9 @@
       <c r="K21" s="33"/>
       <c r="L21" s="33"/>
       <c r="M21" s="33"/>
-    </row>
-    <row r="22" spans="1:13">
+      <c r="N21" s="15"/>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" s="30"/>
       <c r="B22" s="31"/>
       <c r="C22" s="32"/>
@@ -2256,8 +2322,9 @@
       <c r="K22" s="33"/>
       <c r="L22" s="33"/>
       <c r="M22" s="33"/>
-    </row>
-    <row r="23" spans="1:13">
+      <c r="N22" s="15"/>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" s="30"/>
       <c r="B23" s="31"/>
       <c r="C23" s="32"/>
@@ -2271,8 +2338,9 @@
       <c r="K23" s="33"/>
       <c r="L23" s="33"/>
       <c r="M23" s="33"/>
-    </row>
-    <row r="24" spans="1:13">
+      <c r="N23" s="15"/>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" s="30"/>
       <c r="B24" s="31"/>
       <c r="C24" s="32"/>
@@ -2286,8 +2354,9 @@
       <c r="K24" s="33"/>
       <c r="L24" s="33"/>
       <c r="M24" s="33"/>
-    </row>
-    <row r="25" spans="1:13">
+      <c r="N24" s="15"/>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25" s="30"/>
       <c r="B25" s="31"/>
       <c r="C25" s="32"/>
@@ -2301,8 +2370,9 @@
       <c r="K25" s="33"/>
       <c r="L25" s="33"/>
       <c r="M25" s="33"/>
-    </row>
-    <row r="26" spans="1:13">
+      <c r="N25" s="15"/>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26" s="30"/>
       <c r="B26" s="31"/>
       <c r="C26" s="32"/>
@@ -2316,8 +2386,9 @@
       <c r="K26" s="33"/>
       <c r="L26" s="33"/>
       <c r="M26" s="33"/>
-    </row>
-    <row r="27" spans="1:13">
+      <c r="N26" s="15"/>
+    </row>
+    <row r="27" spans="1:14">
       <c r="A27" s="30"/>
       <c r="B27" s="31"/>
       <c r="C27" s="32"/>
@@ -2331,8 +2402,9 @@
       <c r="K27" s="33"/>
       <c r="L27" s="33"/>
       <c r="M27" s="33"/>
-    </row>
-    <row r="28" spans="1:13">
+      <c r="N27" s="15"/>
+    </row>
+    <row r="28" spans="1:14">
       <c r="A28" s="30"/>
       <c r="B28" s="31"/>
       <c r="C28" s="32"/>
@@ -2346,8 +2418,9 @@
       <c r="K28" s="33"/>
       <c r="L28" s="33"/>
       <c r="M28" s="33"/>
-    </row>
-    <row r="29" spans="1:13">
+      <c r="N28" s="15"/>
+    </row>
+    <row r="29" spans="1:14">
       <c r="A29" s="30"/>
       <c r="B29" s="31"/>
       <c r="C29" s="32"/>
@@ -2361,8 +2434,9 @@
       <c r="K29" s="33"/>
       <c r="L29" s="33"/>
       <c r="M29" s="33"/>
-    </row>
-    <row r="30" spans="1:13">
+      <c r="N29" s="15"/>
+    </row>
+    <row r="30" spans="1:14">
       <c r="A30" s="30"/>
       <c r="B30" s="31"/>
       <c r="C30" s="32"/>
@@ -2376,8 +2450,9 @@
       <c r="K30" s="33"/>
       <c r="L30" s="33"/>
       <c r="M30" s="33"/>
-    </row>
-    <row r="31" spans="1:13">
+      <c r="N30" s="15"/>
+    </row>
+    <row r="31" spans="1:14">
       <c r="A31" s="30"/>
       <c r="B31" s="31"/>
       <c r="C31" s="32"/>
@@ -2391,8 +2466,9 @@
       <c r="K31" s="33"/>
       <c r="L31" s="33"/>
       <c r="M31" s="33"/>
-    </row>
-    <row r="32" spans="1:13">
+      <c r="N31" s="15"/>
+    </row>
+    <row r="32" spans="1:14">
       <c r="A32" s="30"/>
       <c r="B32" s="31"/>
       <c r="C32" s="32"/>
@@ -2406,8 +2482,9 @@
       <c r="K32" s="33"/>
       <c r="L32" s="33"/>
       <c r="M32" s="33"/>
-    </row>
-    <row r="33" spans="1:13">
+      <c r="N32" s="15"/>
+    </row>
+    <row r="33" spans="1:14">
       <c r="A33" s="30"/>
       <c r="B33" s="31"/>
       <c r="C33" s="32"/>
@@ -2421,8 +2498,9 @@
       <c r="K33" s="33"/>
       <c r="L33" s="33"/>
       <c r="M33" s="33"/>
-    </row>
-    <row r="34" spans="1:13">
+      <c r="N33" s="15"/>
+    </row>
+    <row r="34" spans="1:14">
       <c r="A34" s="30"/>
       <c r="B34" s="31"/>
       <c r="C34" s="32"/>
@@ -2436,8 +2514,9 @@
       <c r="K34" s="33"/>
       <c r="L34" s="33"/>
       <c r="M34" s="33"/>
-    </row>
-    <row r="35" spans="1:13">
+      <c r="N34" s="15"/>
+    </row>
+    <row r="35" spans="1:14">
       <c r="A35" s="30"/>
       <c r="B35" s="31"/>
       <c r="C35" s="32"/>
@@ -2451,8 +2530,9 @@
       <c r="K35" s="33"/>
       <c r="L35" s="33"/>
       <c r="M35" s="33"/>
-    </row>
-    <row r="36" spans="1:13">
+      <c r="N35" s="15"/>
+    </row>
+    <row r="36" spans="1:14">
       <c r="A36" s="30"/>
       <c r="B36" s="31"/>
       <c r="C36" s="32"/>
@@ -2466,8 +2546,9 @@
       <c r="K36" s="33"/>
       <c r="L36" s="33"/>
       <c r="M36" s="33"/>
-    </row>
-    <row r="37" spans="1:13">
+      <c r="N36" s="15"/>
+    </row>
+    <row r="37" spans="1:14">
       <c r="A37" s="30"/>
       <c r="B37" s="31"/>
       <c r="C37" s="32"/>
@@ -2481,8 +2562,9 @@
       <c r="K37" s="33"/>
       <c r="L37" s="33"/>
       <c r="M37" s="33"/>
-    </row>
-    <row r="38" spans="1:13">
+      <c r="N37" s="15"/>
+    </row>
+    <row r="38" spans="1:14">
       <c r="A38" s="30"/>
       <c r="B38" s="31"/>
       <c r="C38" s="32"/>
@@ -2496,8 +2578,9 @@
       <c r="K38" s="33"/>
       <c r="L38" s="33"/>
       <c r="M38" s="33"/>
-    </row>
-    <row r="39" spans="1:13">
+      <c r="N38" s="15"/>
+    </row>
+    <row r="39" spans="1:14">
       <c r="A39" s="30"/>
       <c r="B39" s="31"/>
       <c r="C39" s="32"/>
@@ -2511,8 +2594,9 @@
       <c r="K39" s="33"/>
       <c r="L39" s="33"/>
       <c r="M39" s="33"/>
-    </row>
-    <row r="40" spans="1:13">
+      <c r="N39" s="15"/>
+    </row>
+    <row r="40" spans="1:14">
       <c r="A40" s="30"/>
       <c r="B40" s="31"/>
       <c r="C40" s="32"/>
@@ -2526,8 +2610,9 @@
       <c r="K40" s="33"/>
       <c r="L40" s="33"/>
       <c r="M40" s="33"/>
-    </row>
-    <row r="41" spans="1:13">
+      <c r="N40" s="15"/>
+    </row>
+    <row r="41" spans="1:14">
       <c r="A41" s="30"/>
       <c r="B41" s="31"/>
       <c r="C41" s="32"/>
@@ -2541,8 +2626,9 @@
       <c r="K41" s="33"/>
       <c r="L41" s="33"/>
       <c r="M41" s="33"/>
-    </row>
-    <row r="42" spans="1:13">
+      <c r="N41" s="15"/>
+    </row>
+    <row r="42" spans="1:14">
       <c r="A42" s="30"/>
       <c r="B42" s="31"/>
       <c r="C42" s="32"/>
@@ -2556,8 +2642,9 @@
       <c r="K42" s="33"/>
       <c r="L42" s="33"/>
       <c r="M42" s="33"/>
-    </row>
-    <row r="43" spans="1:13">
+      <c r="N42" s="15"/>
+    </row>
+    <row r="43" spans="1:14">
       <c r="A43" s="30"/>
       <c r="B43" s="31"/>
       <c r="C43" s="32"/>
@@ -2571,8 +2658,9 @@
       <c r="K43" s="33"/>
       <c r="L43" s="33"/>
       <c r="M43" s="33"/>
-    </row>
-    <row r="44" spans="1:13">
+      <c r="N43" s="15"/>
+    </row>
+    <row r="44" spans="1:14">
       <c r="A44" s="30"/>
       <c r="B44" s="31"/>
       <c r="C44" s="32"/>
@@ -2586,8 +2674,9 @@
       <c r="K44" s="33"/>
       <c r="L44" s="33"/>
       <c r="M44" s="33"/>
-    </row>
-    <row r="45" spans="1:13">
+      <c r="N44" s="15"/>
+    </row>
+    <row r="45" spans="1:14">
       <c r="A45" s="30"/>
       <c r="B45" s="31"/>
       <c r="C45" s="32"/>
@@ -2601,8 +2690,9 @@
       <c r="K45" s="33"/>
       <c r="L45" s="33"/>
       <c r="M45" s="33"/>
-    </row>
-    <row r="46" spans="1:13">
+      <c r="N45" s="15"/>
+    </row>
+    <row r="46" spans="1:14">
       <c r="A46" s="30"/>
       <c r="B46" s="31"/>
       <c r="C46" s="32"/>
@@ -2616,8 +2706,9 @@
       <c r="K46" s="33"/>
       <c r="L46" s="33"/>
       <c r="M46" s="33"/>
-    </row>
-    <row r="47" spans="1:13">
+      <c r="N46" s="15"/>
+    </row>
+    <row r="47" spans="1:14">
       <c r="A47" s="30"/>
       <c r="B47" s="31"/>
       <c r="C47" s="32"/>
@@ -2631,8 +2722,9 @@
       <c r="K47" s="33"/>
       <c r="L47" s="33"/>
       <c r="M47" s="33"/>
-    </row>
-    <row r="48" spans="1:13">
+      <c r="N47" s="15"/>
+    </row>
+    <row r="48" spans="1:14">
       <c r="A48" s="30"/>
       <c r="B48" s="31"/>
       <c r="C48" s="32"/>
@@ -2646,8 +2738,9 @@
       <c r="K48" s="33"/>
       <c r="L48" s="33"/>
       <c r="M48" s="33"/>
-    </row>
-    <row r="49" spans="1:13">
+      <c r="N48" s="15"/>
+    </row>
+    <row r="49" spans="1:14">
       <c r="A49" s="30"/>
       <c r="B49" s="31"/>
       <c r="C49" s="32"/>
@@ -2661,8 +2754,9 @@
       <c r="K49" s="33"/>
       <c r="L49" s="33"/>
       <c r="M49" s="33"/>
-    </row>
-    <row r="50" spans="1:13">
+      <c r="N49" s="15"/>
+    </row>
+    <row r="50" spans="1:14">
       <c r="A50" s="30"/>
       <c r="B50" s="31"/>
       <c r="C50" s="32"/>
@@ -2676,8 +2770,9 @@
       <c r="K50" s="33"/>
       <c r="L50" s="33"/>
       <c r="M50" s="33"/>
-    </row>
-    <row r="51" spans="1:13">
+      <c r="N50" s="15"/>
+    </row>
+    <row r="51" spans="1:14">
       <c r="A51" s="30"/>
       <c r="B51" s="31"/>
       <c r="C51" s="32"/>
@@ -2691,8 +2786,9 @@
       <c r="K51" s="33"/>
       <c r="L51" s="33"/>
       <c r="M51" s="33"/>
-    </row>
-    <row r="52" spans="1:13">
+      <c r="N51" s="15"/>
+    </row>
+    <row r="52" spans="1:14">
       <c r="A52" s="30"/>
       <c r="B52" s="31"/>
       <c r="C52" s="32"/>
@@ -2706,8 +2802,9 @@
       <c r="K52" s="33"/>
       <c r="L52" s="33"/>
       <c r="M52" s="33"/>
-    </row>
-    <row r="53" spans="1:13">
+      <c r="N52" s="15"/>
+    </row>
+    <row r="53" spans="1:14">
       <c r="A53" s="30"/>
       <c r="B53" s="31"/>
       <c r="C53" s="32"/>
@@ -2721,8 +2818,9 @@
       <c r="K53" s="33"/>
       <c r="L53" s="33"/>
       <c r="M53" s="33"/>
-    </row>
-    <row r="54" spans="1:13">
+      <c r="N53" s="15"/>
+    </row>
+    <row r="54" spans="1:14">
       <c r="A54" s="30"/>
       <c r="B54" s="31"/>
       <c r="C54" s="32"/>
@@ -2736,8 +2834,9 @@
       <c r="K54" s="33"/>
       <c r="L54" s="33"/>
       <c r="M54" s="33"/>
-    </row>
-    <row r="55" spans="1:13">
+      <c r="N54" s="15"/>
+    </row>
+    <row r="55" spans="1:14">
       <c r="A55" s="30"/>
       <c r="B55" s="31"/>
       <c r="C55" s="32"/>
@@ -2751,8 +2850,9 @@
       <c r="K55" s="33"/>
       <c r="L55" s="33"/>
       <c r="M55" s="33"/>
-    </row>
-    <row r="56" spans="1:13">
+      <c r="N55" s="15"/>
+    </row>
+    <row r="56" spans="1:14">
       <c r="A56" s="30"/>
       <c r="B56" s="31"/>
       <c r="C56" s="32"/>
@@ -2766,8 +2866,9 @@
       <c r="K56" s="33"/>
       <c r="L56" s="33"/>
       <c r="M56" s="33"/>
-    </row>
-    <row r="57" spans="1:13">
+      <c r="N56" s="15"/>
+    </row>
+    <row r="57" spans="1:14">
       <c r="A57" s="30"/>
       <c r="B57" s="31"/>
       <c r="C57" s="32"/>
@@ -2781,8 +2882,9 @@
       <c r="K57" s="33"/>
       <c r="L57" s="33"/>
       <c r="M57" s="33"/>
-    </row>
-    <row r="58" spans="1:13">
+      <c r="N57" s="15"/>
+    </row>
+    <row r="58" spans="1:14">
       <c r="A58" s="30"/>
       <c r="B58" s="31"/>
       <c r="C58" s="32"/>
@@ -2796,8 +2898,9 @@
       <c r="K58" s="33"/>
       <c r="L58" s="33"/>
       <c r="M58" s="33"/>
-    </row>
-    <row r="59" spans="1:13">
+      <c r="N58" s="15"/>
+    </row>
+    <row r="59" spans="1:14">
       <c r="A59" s="30"/>
       <c r="B59" s="31"/>
       <c r="C59" s="32"/>
@@ -2811,8 +2914,9 @@
       <c r="K59" s="33"/>
       <c r="L59" s="33"/>
       <c r="M59" s="33"/>
-    </row>
-    <row r="60" spans="1:13">
+      <c r="N59" s="15"/>
+    </row>
+    <row r="60" spans="1:14">
       <c r="A60" s="30"/>
       <c r="B60" s="31"/>
       <c r="C60" s="32"/>
@@ -2826,8 +2930,9 @@
       <c r="K60" s="33"/>
       <c r="L60" s="33"/>
       <c r="M60" s="33"/>
-    </row>
-    <row r="61" spans="1:13">
+      <c r="N60" s="15"/>
+    </row>
+    <row r="61" spans="1:14">
       <c r="A61" s="30"/>
       <c r="B61" s="31"/>
       <c r="C61" s="32"/>
@@ -2841,8 +2946,9 @@
       <c r="K61" s="33"/>
       <c r="L61" s="33"/>
       <c r="M61" s="33"/>
-    </row>
-    <row r="62" spans="1:13">
+      <c r="N61" s="15"/>
+    </row>
+    <row r="62" spans="1:14">
       <c r="A62" s="30"/>
       <c r="B62" s="31"/>
       <c r="C62" s="32"/>
@@ -2856,8 +2962,9 @@
       <c r="K62" s="33"/>
       <c r="L62" s="33"/>
       <c r="M62" s="33"/>
-    </row>
-    <row r="63" spans="1:13">
+      <c r="N62" s="15"/>
+    </row>
+    <row r="63" spans="1:14">
       <c r="A63" s="30"/>
       <c r="B63" s="31"/>
       <c r="C63" s="32"/>
@@ -2871,8 +2978,9 @@
       <c r="K63" s="33"/>
       <c r="L63" s="33"/>
       <c r="M63" s="33"/>
-    </row>
-    <row r="64" spans="1:13">
+      <c r="N63" s="15"/>
+    </row>
+    <row r="64" spans="1:14">
       <c r="A64" s="30"/>
       <c r="B64" s="31"/>
       <c r="C64" s="32"/>
@@ -2886,8 +2994,9 @@
       <c r="K64" s="33"/>
       <c r="L64" s="33"/>
       <c r="M64" s="33"/>
-    </row>
-    <row r="65" spans="1:13">
+      <c r="N64" s="15"/>
+    </row>
+    <row r="65" spans="1:14">
       <c r="A65" s="30"/>
       <c r="B65" s="31"/>
       <c r="C65" s="32"/>
@@ -2901,8 +3010,9 @@
       <c r="K65" s="33"/>
       <c r="L65" s="33"/>
       <c r="M65" s="33"/>
-    </row>
-    <row r="66" spans="1:13">
+      <c r="N65" s="15"/>
+    </row>
+    <row r="66" spans="1:14">
       <c r="A66" s="30"/>
       <c r="B66" s="31"/>
       <c r="C66" s="32"/>
@@ -2916,8 +3026,9 @@
       <c r="K66" s="33"/>
       <c r="L66" s="33"/>
       <c r="M66" s="33"/>
-    </row>
-    <row r="67" spans="1:13">
+      <c r="N66" s="15"/>
+    </row>
+    <row r="67" spans="1:14">
       <c r="A67" s="30"/>
       <c r="B67" s="31"/>
       <c r="C67" s="32"/>
@@ -2931,8 +3042,9 @@
       <c r="K67" s="33"/>
       <c r="L67" s="33"/>
       <c r="M67" s="33"/>
-    </row>
-    <row r="68" spans="1:13">
+      <c r="N67" s="15"/>
+    </row>
+    <row r="68" spans="1:14">
       <c r="A68" s="30"/>
       <c r="B68" s="31"/>
       <c r="C68" s="32"/>
@@ -2946,8 +3058,9 @@
       <c r="K68" s="33"/>
       <c r="L68" s="33"/>
       <c r="M68" s="33"/>
-    </row>
-    <row r="69" spans="1:13">
+      <c r="N68" s="15"/>
+    </row>
+    <row r="69" spans="1:14">
       <c r="A69" s="30"/>
       <c r="B69" s="31"/>
       <c r="C69" s="32"/>
@@ -2961,8 +3074,9 @@
       <c r="K69" s="33"/>
       <c r="L69" s="33"/>
       <c r="M69" s="33"/>
-    </row>
-    <row r="70" spans="1:13">
+      <c r="N69" s="15"/>
+    </row>
+    <row r="70" spans="1:14">
       <c r="A70" s="30"/>
       <c r="B70" s="31"/>
       <c r="C70" s="32"/>
@@ -2976,8 +3090,9 @@
       <c r="K70" s="33"/>
       <c r="L70" s="33"/>
       <c r="M70" s="33"/>
-    </row>
-    <row r="71" spans="1:13">
+      <c r="N70" s="15"/>
+    </row>
+    <row r="71" spans="1:14">
       <c r="A71" s="30"/>
       <c r="B71" s="31"/>
       <c r="C71" s="32"/>
@@ -2991,8 +3106,9 @@
       <c r="K71" s="33"/>
       <c r="L71" s="33"/>
       <c r="M71" s="33"/>
-    </row>
-    <row r="72" spans="1:13">
+      <c r="N71" s="15"/>
+    </row>
+    <row r="72" spans="1:14">
       <c r="A72" s="30"/>
       <c r="B72" s="31"/>
       <c r="C72" s="32"/>
@@ -3006,8 +3122,9 @@
       <c r="K72" s="33"/>
       <c r="L72" s="33"/>
       <c r="M72" s="33"/>
-    </row>
-    <row r="73" spans="1:13">
+      <c r="N72" s="15"/>
+    </row>
+    <row r="73" spans="1:14">
       <c r="A73" s="30"/>
       <c r="B73" s="31"/>
       <c r="C73" s="32"/>
@@ -3021,8 +3138,9 @@
       <c r="K73" s="33"/>
       <c r="L73" s="33"/>
       <c r="M73" s="33"/>
-    </row>
-    <row r="74" spans="1:13">
+      <c r="N73" s="15"/>
+    </row>
+    <row r="74" spans="1:14">
       <c r="A74" s="30"/>
       <c r="B74" s="31"/>
       <c r="C74" s="32"/>
@@ -3036,8 +3154,9 @@
       <c r="K74" s="33"/>
       <c r="L74" s="33"/>
       <c r="M74" s="33"/>
-    </row>
-    <row r="75" spans="1:13">
+      <c r="N74" s="15"/>
+    </row>
+    <row r="75" spans="1:14">
       <c r="A75" s="30"/>
       <c r="B75" s="31"/>
       <c r="C75" s="32"/>
@@ -3051,8 +3170,9 @@
       <c r="K75" s="33"/>
       <c r="L75" s="33"/>
       <c r="M75" s="33"/>
-    </row>
-    <row r="76" spans="1:13">
+      <c r="N75" s="15"/>
+    </row>
+    <row r="76" spans="1:14">
       <c r="A76" s="30"/>
       <c r="B76" s="31"/>
       <c r="C76" s="32"/>
@@ -3066,8 +3186,9 @@
       <c r="K76" s="33"/>
       <c r="L76" s="33"/>
       <c r="M76" s="33"/>
-    </row>
-    <row r="77" spans="1:13">
+      <c r="N76" s="15"/>
+    </row>
+    <row r="77" spans="1:14">
       <c r="A77" s="30"/>
       <c r="B77" s="31"/>
       <c r="C77" s="32"/>
@@ -3081,8 +3202,9 @@
       <c r="K77" s="33"/>
       <c r="L77" s="33"/>
       <c r="M77" s="33"/>
-    </row>
-    <row r="78" spans="1:13">
+      <c r="N77" s="15"/>
+    </row>
+    <row r="78" spans="1:14">
       <c r="A78" s="30"/>
       <c r="B78" s="31"/>
       <c r="C78" s="32"/>
@@ -3096,8 +3218,9 @@
       <c r="K78" s="33"/>
       <c r="L78" s="33"/>
       <c r="M78" s="33"/>
-    </row>
-    <row r="79" spans="1:13">
+      <c r="N78" s="15"/>
+    </row>
+    <row r="79" spans="1:14">
       <c r="A79" s="30"/>
       <c r="B79" s="31"/>
       <c r="C79" s="32"/>
@@ -3111,8 +3234,9 @@
       <c r="K79" s="33"/>
       <c r="L79" s="33"/>
       <c r="M79" s="33"/>
-    </row>
-    <row r="80" spans="1:13">
+      <c r="N79" s="15"/>
+    </row>
+    <row r="80" spans="1:14">
       <c r="A80" s="30"/>
       <c r="B80" s="31"/>
       <c r="C80" s="32"/>
@@ -3126,8 +3250,9 @@
       <c r="K80" s="33"/>
       <c r="L80" s="33"/>
       <c r="M80" s="33"/>
-    </row>
-    <row r="81" spans="1:13">
+      <c r="N80" s="15"/>
+    </row>
+    <row r="81" spans="1:14">
       <c r="A81" s="30"/>
       <c r="B81" s="31"/>
       <c r="C81" s="32"/>
@@ -3141,8 +3266,9 @@
       <c r="K81" s="33"/>
       <c r="L81" s="33"/>
       <c r="M81" s="33"/>
-    </row>
-    <row r="82" spans="1:13">
+      <c r="N81" s="15"/>
+    </row>
+    <row r="82" spans="1:14">
       <c r="A82" s="30"/>
       <c r="B82" s="31"/>
       <c r="C82" s="32"/>
@@ -3156,8 +3282,9 @@
       <c r="K82" s="33"/>
       <c r="L82" s="33"/>
       <c r="M82" s="33"/>
-    </row>
-    <row r="83" spans="1:13">
+      <c r="N82" s="15"/>
+    </row>
+    <row r="83" spans="1:14">
       <c r="A83" s="30"/>
       <c r="B83" s="31"/>
       <c r="C83" s="32"/>
@@ -3171,8 +3298,9 @@
       <c r="K83" s="33"/>
       <c r="L83" s="33"/>
       <c r="M83" s="33"/>
-    </row>
-    <row r="84" spans="1:13">
+      <c r="N83" s="15"/>
+    </row>
+    <row r="84" spans="1:14">
       <c r="A84" s="30"/>
       <c r="B84" s="31"/>
       <c r="C84" s="32"/>
@@ -3186,8 +3314,9 @@
       <c r="K84" s="33"/>
       <c r="L84" s="33"/>
       <c r="M84" s="33"/>
-    </row>
-    <row r="85" spans="1:13">
+      <c r="N84" s="15"/>
+    </row>
+    <row r="85" spans="1:14">
       <c r="A85" s="30"/>
       <c r="B85" s="31"/>
       <c r="C85" s="32"/>
@@ -3201,8 +3330,9 @@
       <c r="K85" s="33"/>
       <c r="L85" s="33"/>
       <c r="M85" s="33"/>
-    </row>
-    <row r="86" spans="1:13">
+      <c r="N85" s="15"/>
+    </row>
+    <row r="86" spans="1:14">
       <c r="A86" s="30"/>
       <c r="B86" s="31"/>
       <c r="C86" s="32"/>
@@ -3216,8 +3346,9 @@
       <c r="K86" s="33"/>
       <c r="L86" s="33"/>
       <c r="M86" s="33"/>
-    </row>
-    <row r="87" spans="1:13">
+      <c r="N86" s="15"/>
+    </row>
+    <row r="87" spans="1:14">
       <c r="A87" s="30"/>
       <c r="B87" s="31"/>
       <c r="C87" s="32"/>
@@ -3231,8 +3362,9 @@
       <c r="K87" s="33"/>
       <c r="L87" s="33"/>
       <c r="M87" s="33"/>
-    </row>
-    <row r="88" spans="1:13">
+      <c r="N87" s="15"/>
+    </row>
+    <row r="88" spans="1:14">
       <c r="A88" s="30"/>
       <c r="B88" s="31"/>
       <c r="C88" s="32"/>
@@ -3246,8 +3378,9 @@
       <c r="K88" s="33"/>
       <c r="L88" s="33"/>
       <c r="M88" s="33"/>
-    </row>
-    <row r="89" spans="1:13">
+      <c r="N88" s="15"/>
+    </row>
+    <row r="89" spans="1:14">
       <c r="A89" s="30"/>
       <c r="B89" s="31"/>
       <c r="C89" s="32"/>
@@ -3261,8 +3394,9 @@
       <c r="K89" s="33"/>
       <c r="L89" s="33"/>
       <c r="M89" s="33"/>
-    </row>
-    <row r="90" spans="1:13">
+      <c r="N89" s="15"/>
+    </row>
+    <row r="90" spans="1:14">
       <c r="A90" s="30"/>
       <c r="B90" s="31"/>
       <c r="C90" s="32"/>
@@ -3276,8 +3410,9 @@
       <c r="K90" s="33"/>
       <c r="L90" s="33"/>
       <c r="M90" s="33"/>
-    </row>
-    <row r="91" spans="1:13">
+      <c r="N90" s="15"/>
+    </row>
+    <row r="91" spans="1:14">
       <c r="A91" s="30"/>
       <c r="B91" s="31"/>
       <c r="C91" s="32"/>
@@ -3291,8 +3426,9 @@
       <c r="K91" s="33"/>
       <c r="L91" s="33"/>
       <c r="M91" s="33"/>
-    </row>
-    <row r="92" spans="1:13">
+      <c r="N91" s="15"/>
+    </row>
+    <row r="92" spans="1:14">
       <c r="A92" s="30"/>
       <c r="B92" s="31"/>
       <c r="C92" s="32"/>
@@ -3306,8 +3442,9 @@
       <c r="K92" s="33"/>
       <c r="L92" s="33"/>
       <c r="M92" s="33"/>
-    </row>
-    <row r="93" spans="1:13">
+      <c r="N92" s="15"/>
+    </row>
+    <row r="93" spans="1:14">
       <c r="A93" s="30"/>
       <c r="B93" s="31"/>
       <c r="C93" s="32"/>
@@ -3321,8 +3458,9 @@
       <c r="K93" s="33"/>
       <c r="L93" s="33"/>
       <c r="M93" s="33"/>
-    </row>
-    <row r="94" spans="1:13">
+      <c r="N93" s="15"/>
+    </row>
+    <row r="94" spans="1:14">
       <c r="A94" s="30"/>
       <c r="B94" s="31"/>
       <c r="C94" s="32"/>
@@ -3336,8 +3474,9 @@
       <c r="K94" s="33"/>
       <c r="L94" s="33"/>
       <c r="M94" s="33"/>
-    </row>
-    <row r="95" spans="1:13">
+      <c r="N94" s="15"/>
+    </row>
+    <row r="95" spans="1:14">
       <c r="A95" s="30"/>
       <c r="B95" s="31"/>
       <c r="C95" s="32"/>
@@ -3351,8 +3490,9 @@
       <c r="K95" s="33"/>
       <c r="L95" s="33"/>
       <c r="M95" s="33"/>
-    </row>
-    <row r="96" spans="1:13">
+      <c r="N95" s="15"/>
+    </row>
+    <row r="96" spans="1:14">
       <c r="A96" s="30"/>
       <c r="B96" s="31"/>
       <c r="C96" s="32"/>
@@ -3366,8 +3506,9 @@
       <c r="K96" s="33"/>
       <c r="L96" s="33"/>
       <c r="M96" s="33"/>
-    </row>
-    <row r="97" spans="1:13">
+      <c r="N96" s="15"/>
+    </row>
+    <row r="97" spans="1:14">
       <c r="A97" s="30"/>
       <c r="B97" s="31"/>
       <c r="C97" s="32"/>
@@ -3381,8 +3522,9 @@
       <c r="K97" s="33"/>
       <c r="L97" s="33"/>
       <c r="M97" s="33"/>
-    </row>
-    <row r="98" spans="1:13">
+      <c r="N97" s="15"/>
+    </row>
+    <row r="98" spans="1:14">
       <c r="A98" s="30"/>
       <c r="B98" s="31"/>
       <c r="C98" s="32"/>
@@ -3396,8 +3538,9 @@
       <c r="K98" s="33"/>
       <c r="L98" s="33"/>
       <c r="M98" s="33"/>
-    </row>
-    <row r="99" spans="1:13">
+      <c r="N98" s="15"/>
+    </row>
+    <row r="99" spans="1:14">
       <c r="A99" s="30"/>
       <c r="B99" s="31"/>
       <c r="C99" s="32"/>
@@ -3411,8 +3554,9 @@
       <c r="K99" s="33"/>
       <c r="L99" s="33"/>
       <c r="M99" s="33"/>
-    </row>
-    <row r="100" spans="1:13">
+      <c r="N99" s="15"/>
+    </row>
+    <row r="100" spans="1:14">
       <c r="A100" s="30"/>
       <c r="B100" s="31"/>
       <c r="C100" s="32"/>
@@ -3426,6 +3570,7 @@
       <c r="K100" s="33"/>
       <c r="L100" s="33"/>
       <c r="M100" s="33"/>
+      <c r="N100" s="15"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -3444,7 +3589,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -3453,7 +3598,7 @@
   <sheetData>
     <row r="1" ht="38" customHeight="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3463,66 +3608,98 @@
     </row>
     <row r="3" ht="15" spans="1:6">
       <c r="A3" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1" spans="1:6">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" ht="38" customHeight="1" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" ht="34" customHeight="1" spans="1:6">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" ht="38" customHeight="1" spans="1:6">
       <c r="A5" s="4" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="6" ht="34" customHeight="1" spans="1:6">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" ht="38" customHeight="1" spans="1:6">
       <c r="A6" s="4" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="7" ht="34" customHeight="1" spans="1:6">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" ht="38" customHeight="1" spans="1:6">
       <c r="A7" s="4" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8" ht="34" customHeight="1" spans="1:6">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" ht="38" customHeight="1" spans="1:6">
       <c r="A8" s="4" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="9" ht="34" customHeight="1" spans="1:6">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" ht="38" customHeight="1" spans="1:6">
       <c r="A9" s="4" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="10" ht="34" customHeight="1" spans="1:6">
-      <c r="A10" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>67</v>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" ht="38" customHeight="1" spans="1:6">
+      <c r="A10" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="11" ht="38" customHeight="1" spans="1:6">
+      <c r="A11" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" ht="38" customHeight="1" spans="1:6">
+      <c r="A12" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" ht="38" customHeight="1" spans="1:6">
+      <c r="A13" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" ht="38" customHeight="1" spans="1:6">
+      <c r="A14" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
